--- a/docs/perechen-otchetov/obrazcy/ФО-55.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-55.xlsx
@@ -7,20 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-55" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-55'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +34,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -52,12 +89,27 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -91,56 +143,130 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,245 +632,762 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10.2" customWidth="1" min="8" max="8"/>
+    <col width="10.2" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-55</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>за период с 01.01.2026 по 01.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Заявки на кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>за период с 01.01.2026 по 30.09.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Кредитный специалист</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Стадия</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Заявок</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Запрошено</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Одобрено</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Доля одобренного, %</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Дней в рассмотрении</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Дата решения</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Решение комиссии</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Кредитный договор</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>по заявкам с решением</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>протокол</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>7900</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>4400</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>55.696203</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Кредитование строительных проектов</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="E9" s="14" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Оформлена</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H10" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="I10" s="13" t="n">
         <v>69</v>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Строительство-2026</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>ОсОО «Достук Строй»</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="E11" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H11" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="I11" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="20" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>№ З-2026-000014 от 12.06.2026</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Осмонов Б. Т.</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H12" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="J12" s="32" t="inlineStr">
+        <is>
+          <t>№ 7</t>
+        </is>
+      </c>
+      <c r="K12" s="33" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L12" s="27" t="inlineStr">
+        <is>
+          <t>№ 26-5/090 от 08.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Отклонена</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="17" t="n"/>
+      <c r="L13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>ОсОО «Кут-Мүлк»</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>№ З-2026-000017 от 13.07.2026</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Бекова Н. С.</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" s="32" t="inlineStr">
+        <is>
+          <t>№ 8</t>
+        </is>
+      </c>
+      <c r="K15" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="L15" s="27" t="n"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Поддержка сельхозпроизводителей</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>2900</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>85.294118</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="17" t="n"/>
+      <c r="L16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Оформлена</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>2900</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>85.294118</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="17" t="n"/>
+      <c r="L17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>КФХ «Береке»</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="E18" s="22" t="n">
+        <v>900</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>900</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>900</v>
+      </c>
+      <c r="H18" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="F7" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>ОсОО «Достук Строй» · № 14 от 12.06.2026</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
+      <c r="I18" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>№ З-2026-000011 от 03.06.2026</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Токтогулова Г. А.</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="29" t="n">
+        <v>900</v>
+      </c>
+      <c r="F19" s="29" t="n">
+        <v>900</v>
+      </c>
+      <c r="G19" s="29" t="n">
+        <v>900</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="J19" s="32" t="inlineStr">
+        <is>
+          <t>№ 5</t>
+        </is>
+      </c>
+      <c r="K19" s="33" t="n">
+        <v>46203</v>
+      </c>
+      <c r="L19" s="27" t="inlineStr">
+        <is>
+          <t>№ 26-1/012 от 14.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>ОсОО «Чүй-Тамак»</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Агро-2026</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+      <c r="E20" s="22" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>№ З-2026-000016 от 06.07.2026</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Бекова Н. С.</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="29" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G21" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H21" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="I21" s="31" t="n">
+        <v>31</v>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>№ 6</t>
+        </is>
+      </c>
+      <c r="K21" s="33" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L21" s="27" t="inlineStr">
+        <is>
+          <t>№ 26-3/118 от 20.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Без программы (индивидуальная заявка)</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>900000</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Одобрена</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
+      <c r="E22" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="34" t="n"/>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="J22" s="16" t="n"/>
+      <c r="K22" s="17" t="n"/>
+      <c r="L22" s="12" t="n"/>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>900000</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>КФХ «Береке» · № 11 от 03.06.2026</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
+      <c r="E23" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="34" t="n"/>
+      <c r="H23" s="34" t="n"/>
+      <c r="I23" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="J23" s="16" t="n"/>
+      <c r="K23" s="17" t="n"/>
+      <c r="L23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>ОсОО «Каракол-Сервис»</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>900000</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
+      <c r="E24" s="22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="20" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>№ З-2026-000021 от 01.09.2026</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Токтогулова Г. А.</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Комиссия (предварительно)</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="29" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="31" t="n">
+        <v>29</v>
+      </c>
+      <c r="J25" s="32" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="27" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="12">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-55 · сформировал Ибраимова Г. Т. 06.10.2026 10:40 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -754,7 +1397,177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="38" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>ФО-55 «Заявки на кредит за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>01.01.2026 – 30.09.2026 (по умолчанию — с начала года по вчерашний день)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Что попадает</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>заявки, которые были в работе хотя бы один день периода: поданы не позже 30.09.2026 и не оформлены, не отклонены и не отозваны до 01.01.2026; программа, статус, стадия, специалист и дни в рассмотрении — на 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Доля одобренного</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>одобрено ÷ запрошено по заявкам с решением комиссии (одобренные и отклонённые); заявки до решения и отозванные в долю не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Кредитная программа → Статус заявки → Заёмщик → заявка</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>USD — 87,50000, EUR — 101,50000 на 30.09.2026; заявок в иностранной валюте в отчёте нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>Период закрыт</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Ибраимова Г. Т.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39" customHeight="1">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками, проценты — с одним знаком. Итоги и проценты считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -763,372 +1576,532 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>ФО-55 «Заявки по программам и статусам» — карточка</t>
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>ФО-55 «Заявки на кредит за период» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>ФО-55</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Заявки по программам и статусам</t>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>Заявки на кредит за период</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Заявка и комиссия</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>ТЗ 02; ТЗ 03</t>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>ТЗ 02; ТЗ 03; ТЗ 20 п. 13.14</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="135" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Руководству и кредитным специалистам — сколько заявок подано по каждой программе, в каком они статусе и какая часть запрошенных сумм одобрена.</t>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>Правлению, руководству Департамента администрирования кредитов и Департамента регионального развития и кредитным специалистам — сколько заявок на кредит прошло за период по каждой кредитной программе, где каждая стоит на конец периода (статус и стадия), сколько запрошено и сколько одобрено комиссией, какая доля запрошенного одобрена по рассмотренным заявкам и как долго шло рассмотрение. Это список заявок за плитками дашборда «Заявок в работе», «На рассмотрении», «Подано заявок». Кредитный специалист видит только свои заявки. Протокол заседания по одной заявке — бланк ФО-63; заявки в нагрузке специалистов — ФО-25; выдача по одобренным заявкам — ФО-08 и ФО-56. Новая форма: в старой системе отчёта по заявкам не было; прежнее название в перечне — «Заявки по программам и статусам» (общий стартовый отчёт ТЗ 20).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>За период по дате подачи; по требованию. Для общего ежемесячного обзора период — с начала года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>За период, по требованию; по умолчанию — с начала года по вчерашний день. Можно выбрать любой период.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="165" customHeight="1">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>• Период подачи — с начала года
-• Программа — все
-• Статус — все</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>• Период — с начала года по вчерашний день; можно выбрать любой. В отчёт попадает заявка, которая была в работе хотя бы один день периода: подана (получила номер) не позже конца периода и не оформлена, не отклонена и не отозвана до его начала
+• Разрезы — до шести уровней в любом порядке; по умолчанию кредитная программа → статус заявки → заёмщик → заявка. Доступны: кредитная программа, статус заявки, стадия, департамент, кредитный специалист, область, район, месяц подачи, валюта, заёмщик
+• Отбор — по любому из разрезов; поданные в периоде; с решением комиссии в периоде; только в работе на конец периода (не оформлены, не отклонены и не отозваны)
+• Единица — тыс. сом; можно выбрать сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="255" customHeight="1">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Программа → статус заявки → заявка. Подытоги по программе и статусу, сверху ИТОГО. Программы — по убыванию запрошенной суммы; статусы — по порядку жизненного цикла заявки (Новый, На рассмотрении, Требуется доп. информация, Одобрена, Отклонена, Ожидает решения/программы, На оформлении, Оформлена, Отозвана). Доля одобренного считается из сумм уровня.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>Строка детали — заявка на кредит «№ З-ГГГГ-NNNNNN от ДД.ММ.ГГГГ» (структурный номер и дата подачи); над ней всегда строка заёмщика (заявителя), даже при одной заявке. Над заёмщиками — разрезы, по умолчанию кредитная программа → статус заявки. Программа, статус, стадия, кредитный специалист и его департамент — на конец периода у модуля «Заявки»; отчёт их не вычисляет. Заявка без программы (индивидуальная) стоит в группе «Без программы (индивидуальная заявка)», после привязки программы — под программой. Область и район — заявителя, департамент — кредитного специалиста. Черновик до подачи номера не имеет и в отчёт не входит; заявка, пересозданная после отклонения или отзыва, — новая строка с новым номером. Первая строка — ИТОГО; строка разреза несёт число заявок, суммы, долю одобренного и наибольший срок рассмотрения и стоит над своими строками. Доля одобренного — по суммам строки и только по заявкам с решением комиссии (одобренные в любом следующем статусе и отклонённые): заявки до решения и отозванные в неё не входят. Порядок: программы — по алфавиту, «Без программы» — последней; статусы — по ходу заявки (Новый → На рассмотрении → Требуется доп. информация → Одобрена → Ожидает решения/программы → На оформлении → Оформлена → Отклонена → Отозвана), пустые не показываются; заёмщики — по алфавиту наименования без организационной формы; заявки — по дате подачи. Заявка в иностранной валюте — запрошено и одобрено в сомах по курсу последнего дня периода, под заявкой курсивом строка «в тыс. USD (курс …)», в итоги не входит. Печать — A4 альбомная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>по умолчанию: Кредитная программа → Статус заявки → Заёмщик → заявка; можно выбрать: Кредитная программа, Статус заявки, Стадия, Департамент, Кредитный специалист, Область, Район, Месяц подачи, Валюта, Заёмщик</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>Заявок на кредит за период по условиям отбора нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Заявки по программам и статусам»; в старой системе отчёта по заявкам не было. Строка — заявка под кредитной программой, статусом и заёмщиком: кредитный специалист, стадия, запрошено, одобрено комиссией, доля одобренного по заявкам с решением, дни в рассмотрении, протокол и кредитный договор; заявки в нагрузке специалистов — ФО-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr"/>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>программа, статус или заёмщик с номером и датой заявки — по уровню строки</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="B22" s="42" t="inlineStr"/>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>кредитная программа, статус заявки, заёмщик или заявка «№ З-ГГГГ-NNNNNN от ДД.ММ.ГГГГ» (структурный номер, дата подачи) — по уровню строки</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>Кредитный специалист</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr"/>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>специалист заявки на конец периода (роль «специалист заявки» в кураторстве); у строк разрезов пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Стадия</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr"/>
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>узел комплектации на конец периода у заявки до решения (Новый, Требуется доп. информация, На рассмотрении): «Комплектация», «Подтверждение ГФ», «Заключения отделов», «Комиссия (предварительно)», «Комитет · решение» — как отдаёт модуль «Заявки»; у заявки с решением и у отозванной пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>Заявок</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr"/>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>число заявок в строке</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="B25" s="42" t="inlineStr"/>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>число заявок; у заявки пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>Запрошено</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr"/>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>сумма, запрошенная заявителем, сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="C26" s="42" t="inlineStr">
+        <is>
+          <t>сумма, запрошенная заявителем (слой заёмщика в условиях заявки), на конец периода</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>по заявкам с решением</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>Запрошено</t>
+        </is>
+      </c>
+      <c r="C27" s="42" t="inlineStr">
+        <is>
+          <t>запрошено по заявкам с решением комиссии — одобренным (одобрена, ожидает решения/программы, на оформлении, оформлена) и отклонённым; у заявки без решения и в строке, где решений нет, — пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>Одобрено</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr"/>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>сумма, одобренная решением комиссии, сом; до решения — 0,00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr"/>
+      <c r="C28" s="42" t="inlineStr">
+        <is>
+          <t>сумма, одобренная комиссией (слой комиссии в условиях заявки); у отклонённой — 0,00; у заявки без решения — пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>Доля одобренного, %</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr"/>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>одобрено / запрошено × 100, один знак; на каждом уровне из сумм уровня</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B29" s="42" t="inlineStr"/>
+      <c r="C29" s="42" t="inlineStr">
+        <is>
+          <t>одобрено ÷ запрошено по заявкам с решением × 100 — по суммам строки на каждом уровне, не среднее долей; пусто, если в строке нет решений</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>Дней в рассмотрении</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr"/>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>дни от даты подачи до решения комиссии (для заявки без решения — до даты отчёта); в итоговых строках — наибольшее</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Дата решения</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr"/>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>дата решения комиссии; пусто, если решения нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="B30" s="42" t="inlineStr"/>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>от даты подачи до решения комиссии; без решения — до конца периода, у отозванной — до отзыва; в строке разреза — наибольшее</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>протокол</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>Решение комиссии</t>
+        </is>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>номер протокола заседания комиссии, на котором вынесено решение; у заявки без решения пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>Решение комиссии</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>дата заседания, на котором вынесено решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>Кредитный договор</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="inlineStr"/>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>кредит, сформированный по заявке, «№ … от …» — у заявки на оформлении и оформленной; у строк разрезов пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
         <is>
           <t>Правила проверки</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>За 01.01.2026–30.09.2026 по всему набору: 5 заявок — 3 оформлены (КЗ-17, КЗ-18, КЗ-26), 1 отклонена (КЗ-11), 1 на рассмотрении (КЗ-20); запрошено 9 100,000 тыс. сом, по заявкам с решением 7 900,000, одобрено 4 400,000, доля одобренного 55,7 %; наибольший срок рассмотрения — 69 дней (КЗ-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>„Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>КЗ-17 ОсОО «Достук Строй»: заявка № З-2026-000014 от 12.06.2026 по программе «Кредитование строительных проектов», возвращена на доработку 26.06.2026 (ФО-90), решение — протокол № 7 от 20.08.2026 (ФО-63), 69 дней; запрошено и одобрено 1 500,000 = сумма кредита № 26-5/090 от 08.09.2026 (основание в ФО-09 — «Заявка № 14 · протокол комиссии № 7»); «Оформлена» с 08.09.2026 — регистрация кредита в ФО-58.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>КЗ-26 ОсОО «Чүй-Тамак»: заявка № З-2026-000016 от 06.07.2026 — запрошено 2 500,000, комиссия одобрила 2 000,000 (протокол № 6 от 06.08.2026, 31 день), доля 80,0 %; одобренное = сумма кредита № 26-3/118 от 20.08.2026 (ФО-08). Освоения нет, но заявка «Оформлена»: выдачу показывают ФО-08 и ФО-56.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>КЗ-18 КФХ «Береке»: заявка № З-2026-000011 от 03.06.2026 — протокол № 5 от 30.06.2026, 27 дней, одобрено 900,000; кредит № 26-1/012 от 14.07.2026 расторгнут 10.09.2026 без выдачи средств (ФО-58, ФО-84) — заявка остаётся «Оформлена»: судьба кредита статус заявки не меняет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="41" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>КЗ-11 ОсОО «Кут-Мүлк»: заявка № З-2026-000017 от 13.07.2026 на 3 000,000 отклонена (протокол № 8 от 27.08.2026, 45 дней) — одобрено 0,00 и в долю входит: по программе «Кредитование строительных проектов» 1 500,000 ÷ 4 500,000 = 33,3 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>КЗ-20 ОсОО «Каракол-Сервис»: индивидуальная заявка № З-2026-000021 от 01.09.2026 без программы — в группе «Без программы (индивидуальная заявка)»; отправлена в комиссию 24.09.2026, на 30.09.2026 «На рассмотрении», стадия «Комиссия (предварительно)», 29 дней; «по заявкам с решением», «Одобрено» и доля пусты — решения нет. В ФО-25 на 01.10.2026 — заявка в работе у Токтогуловой Г. А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>За сентябрь 2026 (01.09–30.09): 2 заявки — КЗ-17 (на оформлении до 08.09.2026) и КЗ-20; КЗ-18, КЗ-26 и КЗ-11 закрыты до начала периода. С отбором «поданные в периоде» — 1 (КЗ-20), «с решением комиссии в периоде» — 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>Строка разреза = сумма строк на уровень ниже по «Заявок», «Запрошено» и «Одобрено»; доля — из сумм строки, не среднее долей; дней в рассмотрении — наибольшее.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
